--- a/Google classroom8.xlsx
+++ b/Google classroom8.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Test the Web Application Functionality of Google Classroom.</t>
-  </si>
-  <si>
-    <t>Google Classroom Web Application</t>
   </si>
   <si>
     <t>Open Google Classroom.</t>
@@ -170,9 +167,6 @@
     <t>Verify sign out successfully.</t>
   </si>
   <si>
-    <t>1. Verify Google Classroom Login.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Enter valid credentials and click </t>
     </r>
@@ -239,30 +233,6 @@
         <family val="2"/>
       </rPr>
       <t>Stream.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Click </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Announce something</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and post</t>
     </r>
   </si>
   <si>
@@ -348,6 +318,42 @@
   </si>
   <si>
     <t>TC_Practical-008</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Announce something</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and post.</t>
+    </r>
+  </si>
+  <si>
+    <t>Access to internet.</t>
+  </si>
+  <si>
+    <t>Chrome Browser.</t>
+  </si>
+  <si>
+    <t>1. Verify Google Classroom Web Application.</t>
+  </si>
+  <si>
+    <t>Windows OS</t>
   </si>
 </sst>
 </file>
@@ -883,6 +889,100 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>504825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1171575</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1600200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1025" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2952750" y="4800600"/>
+          <a:ext cx="1952625" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>390525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1228725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1666876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect l="30765" t="11110" r="3860" b="8492"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2962275" y="6410325"/>
+          <a:ext cx="2000250" cy="1276351"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
@@ -1107,7 +1207,7 @@
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -1142,14 +1242,14 @@
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="28" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="43" t="s">
@@ -1275,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C6" s="29"/>
       <c r="D6" s="30"/>
@@ -1307,7 +1407,9 @@
       <c r="A7" s="19">
         <v>2</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="28" t="s">
+        <v>64</v>
+      </c>
       <c r="C7" s="29"/>
       <c r="D7" s="30"/>
       <c r="E7" s="8"/>
@@ -1338,7 +1440,9 @@
       <c r="A8" s="19">
         <v>3</v>
       </c>
-      <c r="B8" s="28"/>
+      <c r="B8" s="28" t="s">
+        <v>66</v>
+      </c>
       <c r="C8" s="29"/>
       <c r="D8" s="30"/>
       <c r="E8" s="8"/>
@@ -1428,7 +1532,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C11" s="47"/>
       <c r="D11" s="47"/>
@@ -1545,16 +1649,16 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" spans="1:25" ht="33.75" customHeight="1">
+    <row r="15" spans="1:25" ht="135.75" customHeight="1">
       <c r="A15" s="19">
         <v>1</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="30"/>
       <c r="D15" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="28"/>
@@ -1578,16 +1682,16 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" spans="1:25" ht="42.75" customHeight="1">
+    <row r="16" spans="1:25" ht="140.25" customHeight="1">
       <c r="A16" s="19">
         <v>2</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="30"/>
       <c r="F16" s="28"/>
@@ -1616,11 +1720,11 @@
         <v>3</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="30"/>
       <c r="F17" s="28"/>
@@ -1649,11 +1753,11 @@
         <v>4</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="28"/>
@@ -1682,11 +1786,11 @@
         <v>5</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="30"/>
       <c r="D19" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="28"/>
@@ -1715,11 +1819,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="30"/>
       <c r="F20" s="28"/>
@@ -1748,11 +1852,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" s="30"/>
       <c r="F21" s="28"/>
@@ -1781,11 +1885,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" s="30"/>
       <c r="F22" s="28"/>
@@ -1814,11 +1918,11 @@
         <v>9</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="30"/>
       <c r="D23" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="30"/>
       <c r="F23" s="28"/>
@@ -1847,11 +1951,11 @@
         <v>10</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="28"/>
@@ -1880,11 +1984,11 @@
         <v>11</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="30"/>
       <c r="F25" s="28"/>
@@ -1913,11 +2017,11 @@
         <v>12</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C26" s="30"/>
       <c r="D26" s="28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="30"/>
       <c r="F26" s="28"/>
@@ -1946,11 +2050,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" s="30"/>
       <c r="F27" s="28"/>
@@ -1979,11 +2083,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" s="30"/>
       <c r="F28" s="28"/>
@@ -2012,11 +2116,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="30"/>
       <c r="F29" s="28"/>
@@ -2045,11 +2149,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="28"/>
@@ -2078,11 +2182,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="30"/>
       <c r="F31" s="28"/>
@@ -2111,11 +2215,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="30"/>
       <c r="D32" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="30"/>
       <c r="F32" s="28"/>
@@ -2144,11 +2248,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="30"/>
       <c r="D33" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="28"/>
@@ -2177,11 +2281,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="33"/>
       <c r="D34" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="33"/>
       <c r="F34" s="32"/>
@@ -2210,11 +2314,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C35" s="33"/>
       <c r="D35" s="32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" s="33"/>
       <c r="F35" s="32"/>
@@ -28244,5 +28348,6 @@
   </mergeCells>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>